--- a/shiti/普工试题(1).xlsx
+++ b/shiti/普工试题(1).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="87">
   <si>
     <t>题目类型</t>
   </si>
@@ -72,592 +72,88 @@
     <t>判断题</t>
   </si>
   <si>
-    <t>进入施工现场前，所有作业人员必须接受三级安全培训，考试合格后方可作业。</t>
-  </si>
-  <si>
     <t>对</t>
   </si>
   <si>
-    <t>新员工入场前必须进行体检，患有高血压的人可以从事高空作业。</t>
-  </si>
-  <si>
     <t>错</t>
   </si>
   <si>
-    <t>安全帽佩戴时可以不系帽带，只要戴在头上就行。</t>
-  </si>
-  <si>
     <t>未系好帽带等于没戴安全帽，必须系紧下颌带。</t>
   </si>
   <si>
-    <t>进入施工现场可以穿拖鞋或凉鞋，只要不影响工作即可。</t>
-  </si>
-  <si>
     <t>进入施工现场必须穿劳保鞋，禁止穿拖鞋、凉鞋、高跟鞋等进入施工现场</t>
   </si>
   <si>
-    <t>施工现场严禁吸烟，违者将受到处罚。</t>
-  </si>
-  <si>
-    <t>进入受限空间作业可以使用过滤式防毒面具。</t>
-  </si>
-  <si>
     <t>应使用送风式长管面具或正压式空气呼吸器。</t>
   </si>
   <si>
-    <t>进入受限空间作业前必须进行气体分析，合格后方可进入。</t>
-  </si>
-  <si>
-    <t>厂区内驾驶车辆可以接打手机，只要注意安全即可。</t>
-  </si>
-  <si>
     <t>禁止驾车、骑车人员接打手机。</t>
   </si>
   <si>
-    <t>偷盗物资价值100元以下的，罚款2000元并予以辞退。</t>
-  </si>
-  <si>
-    <t>高处作业时可以使用绳子代替安全带。</t>
-  </si>
-  <si>
-    <t>高空作业时可以将工具随意放置在高处边缘。</t>
-  </si>
-  <si>
-    <t>六级及以上大风天气应停止露天高空作业。</t>
-  </si>
-  <si>
-    <t>起重作业时，吊物下方严禁人员通过或逗留。</t>
-  </si>
-  <si>
-    <t>起重作业可以由多人同时指挥，以提高效率。</t>
-  </si>
-  <si>
     <t>严禁多人一同指挥起重吊装作业。</t>
   </si>
   <si>
-    <t>动火作业时必须佩戴防护眼镜或面罩。</t>
-  </si>
-  <si>
-    <t>气瓶可以在高温环境下暴晒。</t>
-  </si>
-  <si>
     <t>气瓶应避免暴晒，防止过热超压，发生爆炸。</t>
   </si>
   <si>
-    <t>干粉灭火器使用前需要上下颠倒几次。</t>
-  </si>
-  <si>
-    <t>灭火器压力表指针在红色区域表示正常。</t>
-  </si>
-  <si>
     <t>绿色区域表示压力正常，红色区域表示压力不足。</t>
   </si>
   <si>
-    <t>起重作业中，钢丝绳可以与物体的棱角直接接触。</t>
-  </si>
-  <si>
     <t>在棱角处采取加垫或包角措施。</t>
   </si>
   <si>
-    <t>卸卡可以横向受力使用。</t>
-  </si>
-  <si>
     <t>卸卡不得横向受力。</t>
   </si>
   <si>
-    <t>现场所有安全设施可以随意拆除，消防器材可以随意挪动使用，只要事后恢复即可。</t>
-  </si>
-  <si>
     <t>安全设施不得私自移动或拆除，必须办理手续。</t>
   </si>
   <si>
-    <t>进入施工现场必须穿反光背心和劳保鞋。</t>
-  </si>
-  <si>
-    <t>射线探伤作业对人体没有伤害。</t>
-  </si>
-  <si>
     <t>射线探伤可能引起放射线伤害，严重时可致死。</t>
   </si>
   <si>
-    <t>工完料尽场地清是文明施工的要求。</t>
-  </si>
-  <si>
-    <t>宿舍内可以使用煤气罐和大功率电器。</t>
-  </si>
-  <si>
     <t>宿舍禁止使用煤气罐、大功率用电器。</t>
   </si>
   <si>
-    <t>员工可以躺在床上吸烟。</t>
-  </si>
-  <si>
-    <t>动土作业前不需要办理作业许可证，只要现场负责人同意即可施工。</t>
-  </si>
-  <si>
     <t>根据《化学品生产单位特殊作业安全规范》（GB 30871），动土作业属于特殊作业，必须办理《动土作业许可证》，经审批后方可施工。</t>
   </si>
   <si>
-    <t>动土作业前应查明地下设施（如电缆、管道等）的位置，并采取保护措施。</t>
-  </si>
-  <si>
-    <t>动土作业现场应设置警戒线和警示标志，夜间应设红灯警示。</t>
-  </si>
-  <si>
-    <t>动土作业时，挖出的泥土可以堆放在基坑边缘，不需考虑堆土距离。</t>
-  </si>
-  <si>
     <t>动土作业操作规程要求，挖出的泥土应堆放在距坑边至少0.8米以外，高度不超过1.5米，防止坍塌。</t>
   </si>
   <si>
-    <t>打开有毒有害介质管线时，可以不佩戴呼吸防护用品，只要通风良好即可。</t>
-  </si>
-  <si>
     <t>涉及有毒有害介质时，作业人员必须佩戴合适的呼吸防护用品（如空气呼吸器），不能仅依赖通风。</t>
   </si>
   <si>
-    <t>管线打开前应确认管线已泄压、排空、隔离，并进行气体检测。</t>
-  </si>
-  <si>
-    <t>管线打开作业时，可以使用普通工具敲击螺栓，不需要防爆工具</t>
-  </si>
-  <si>
     <t>在易燃易爆场所进行管线打开作业，应使用防爆工具，防止产生火花引发爆炸</t>
   </si>
   <si>
-    <t>管线打开作业完成后，应及时恢复并确认无泄漏。</t>
-  </si>
-  <si>
-    <t>管线打开时，可以先拆开螺栓，再确认是否还有压力</t>
-  </si>
-  <si>
     <t>必须先确认管线已完全泄压，方可进行拆解作业，严禁带压拆解螺栓。</t>
   </si>
   <si>
-    <t>打开涉及高温介质的管线时，应穿戴好防烫防护用品。</t>
-  </si>
-  <si>
-    <t>盲板抽堵作业应办理《盲板抽堵作业许可证》，并经审批。</t>
-  </si>
-  <si>
-    <t>盲板抽堵作业前应进行气体检测，合格后方可作业。</t>
-  </si>
-  <si>
     <t>盲板抽堵作业前，必须对作业环境进行气体检测，确保无爆炸性、有毒有害气体。</t>
   </si>
   <si>
-    <t>盲板抽堵作业时，作业人员应站在上风向。</t>
-  </si>
-  <si>
-    <t>盲板抽堵作业可以不设监护人，由作业人员自行负责。</t>
-  </si>
-  <si>
     <t>盲板抽堵作业必须设专人监护，监护人不得离开现场。</t>
   </si>
   <si>
-    <t>盲板应挂牌标识，内容包括盲板编号、位置、操作人等。</t>
-  </si>
-  <si>
     <t>盲板安装后应挂牌标识，内容包括盲板编号、位置、操作人、日期等信息。</t>
   </si>
   <si>
-    <t>同一管线多个盲板抽堵作业可以同时进行，不需要分别确认。</t>
-  </si>
-  <si>
     <t>每一处盲板抽堵作业都应单独确认安全条件，严禁盲目同时操作多个点位。</t>
   </si>
   <si>
-    <t>国家法律明文规定，劳动者有拒绝违章指挥和强令冒险作业的权利。</t>
-  </si>
-  <si>
-    <t>“四不伤害”是指不伤害自己、不伤害别人、不被别人伤害、保护他人不受伤害。</t>
-  </si>
-  <si>
-    <t>从业人员有权对本单位安全生产工作存在问题提出批评、检举、控告。</t>
-  </si>
-  <si>
-    <t>焊工、架子工、起重工、电工等特种作业人员无证上岗不构成违法行为。</t>
-  </si>
-  <si>
-    <t>员工有权拒绝危险作业。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>一个开关可以直接控制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>台用电设备。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>在基准面</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>米以上进行登高作业不需要采取防坠落措施。</t>
-    </r>
-  </si>
-  <si>
-    <t>严禁任何人攀登吊运中的物体或在吊物下穿行与逗留。</t>
-  </si>
-  <si>
-    <t>漏电保护器发生掉闸时不能强行合闸，应由电工查明原因排除故障后，才能继续使用。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>禁止在阵风风力达六级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>风速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10.8m/s)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>以上及雨、雪天气情况时进行高处作业。</t>
-    </r>
-  </si>
-  <si>
-    <t>高处动火，作业点下方可以放置可燃物且不用采取火花收集措施。</t>
-  </si>
-  <si>
-    <t>使用脚手架或梯子进行高处作业，要将其固定防止倾倒，严禁带人移动。</t>
-  </si>
-  <si>
-    <t>脚手架搭设应设置扫地杆、剪刀撑，当脚手架较高时应设置抛撑以防止倾倒。</t>
-  </si>
-  <si>
-    <t>安全带应高挂低用，不得采用低于肩部水平的系挂方法。严禁用绳子捆在腰部代替安全带或仅在腰部系扎一字型安全带。</t>
-  </si>
-  <si>
-    <t>在使用手电钻、电砂轮等手持电动工具前，不需要由电工检测和张贴合格标签。</t>
-  </si>
-  <si>
-    <t>作业人员严禁酒后上岗作业，施工现场严禁吸烟，禁止在施工现场追逐打闹。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>不得在动火点</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>米范围内及动火点下方同时进行可燃溶剂清洗或喷漆作业。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>铺设脚手架架板时必须使用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12#</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>镀锌丝对架板进行有效固定。</t>
-    </r>
-  </si>
-  <si>
-    <t>在高处作业时允许上下作业人员之间相互投掷材料、工具。</t>
-  </si>
-  <si>
-    <t>登高作业必须系挂安全带且高挂低用，严禁在没有扶手的攀沿物上随意走动。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>脚手架平台四周必须分别设</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>米和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>米高的护栏，并在平台四边设置不低于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>厘米高的踢脚板。</t>
-    </r>
-  </si>
-  <si>
-    <t>使用圆锯、砂轮、风镐进行切削、破碎、锤击等产生火花的作业必须佩带护目镜。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>在大风（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>级风及以上）或雷雨等恶劣天气情况下，禁止在室外使用脚手架。</t>
-    </r>
-  </si>
-  <si>
-    <t>脚手架必须设有垫板，可以使用桶、砖块或石块等不稳定物体作为脚手架垫板。</t>
-  </si>
-  <si>
-    <t>钢筋加工机械（如弯曲机、切断机）运行时，操作人员可以戴手套调整钢筋位置。</t>
-  </si>
-  <si>
-    <t>发现钢筋加工机械出现异常响声或卡顿时，应立即停机并联系维修人员检查。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>切割钢筋时产生的飞溅火花无需佩戴护目镜，只需侧身操作即可</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>。</t>
-    </r>
-  </si>
-  <si>
-    <t>钢筋工结束作业后，需关闭所有设备电源，清理现场并检查有无火灾隐患。</t>
-  </si>
-  <si>
-    <t>钢筋加工区域内的废料应及时清理，但尖锐铁屑可直接堆放在通道旁。</t>
-  </si>
-  <si>
-    <t>钢筋弯曲机运行时，若钢筋卡住，可用脚踩住钢筋强行调整。</t>
-  </si>
-  <si>
-    <t>安全带、安全帽、救生索等设备使用前，必须进行检查，不得存在如焊接损坏、化学腐蚀、机械损伤等状况。</t>
-  </si>
-  <si>
-    <t>管工在安装或维修管道时，可以不切断相关介质的来源，只要操作熟练即可。</t>
-  </si>
-  <si>
     <t>在维修或安装涉及介质（水、气、油、化学品等）的管道时，必须切断介质来源、泄压、排空，并采取隔离措施，严禁带压或带介质操作。</t>
   </si>
   <si>
-    <t>管工使用手持电动工具（如电钻、磨光机）时，可以不使用漏电保护器。</t>
-  </si>
-  <si>
     <t>手持电动工具必须配备漏电保护器，并确保接地良好。</t>
   </si>
   <si>
-    <t>管工可以使用破损或磨损严重的管钳、扳手等工具，只要还能勉强使用。</t>
-  </si>
-  <si>
     <t>生产经营单位必须提供符合国家标准或者行业标准的劳动防护用品和工具，严禁使用破损、不合格的工具。</t>
   </si>
   <si>
-    <t>管工在沟槽内作业时，应检查沟壁是否稳定，必要时采取支护措施。</t>
-  </si>
-  <si>
-    <t>管工作业结束后，应清理现场，做到工完料尽场地清。</t>
-  </si>
-  <si>
-    <t>管工在安装有压管道时，可以使用强力强行调整管道对口，即使管道存在较大偏差。</t>
-  </si>
-  <si>
     <t>管道对口时应采用适当方法调整偏差，严禁强力对口，防止管道产生过大应力，导致焊缝开裂或介质泄漏事故。</t>
   </si>
   <si>
-    <t>管工在拆除旧管道时，可以直接切割或拆卸，不需确认管道内是否残留介质。</t>
-  </si>
-  <si>
     <t>拆除管道前必须确认管道内介质已排空、清洗置换合格，并采取隔离措施，严禁带介质、带压切割或拆卸。</t>
-  </si>
-  <si>
-    <t>管工在进行管道试压时，可以站在堵头或盲板的正前方观察压力变化。</t>
   </si>
   <si>
     <t>管道试压时，严禁人员站在堵头、盲板或法兰的正前方，防止试压过程中堵头飞出伤人。</t>
@@ -1568,7 +1064,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1657,9 +1153,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1983,11 +1476,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L82"/>
-  <sheetFormatPr defaultColWidth="10.6916666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="10.6909090909091" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10.6916666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="162.75" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="10.6916666666667" style="2" customWidth="1"/>
+    <col min="1" max="1" width="10.6909090909091" style="1" customWidth="1"/>
+    <col min="2" max="2" width="162.754545454545" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="10.6909090909091" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="26" customFormat="1" ht="21" customHeight="1" spans="1:12">
@@ -2028,976 +1521,976 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="18.75" spans="1:12">
+    <row r="2" ht="17.5" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>13</v>
+      <c r="B2" s="28">
+        <v>1</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" spans="1:12">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" ht="17.5" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="28">
+        <v>2</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" ht="17.5" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="28">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D4" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="17.5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="28">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="30" t="s">
+      <c r="D5" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="17.5" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="28">
+        <v>5</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" ht="17.5" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="28">
+        <v>6</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D7" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" ht="17.5" spans="1:12">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="28">
+        <v>7</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="17.5" spans="1:12">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="28">
+        <v>8</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D9" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="17.5" spans="1:12">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="28">
+        <v>9</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="17.5" spans="1:12">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="28">
+        <v>10</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="17.5" spans="1:12">
+      <c r="A12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="28">
+        <v>11</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="17.5" spans="1:12">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28">
+        <v>12</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="17.5" spans="1:12">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="28">
+        <v>13</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="17.5" spans="1:12">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="28">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="17.5" spans="1:12">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="28">
+        <v>15</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="17.5" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="28">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" ht="18.75" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="28" t="s">
+      <c r="C17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" ht="17.5" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="28">
+        <v>17</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" ht="17.5" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="28">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" ht="17.5" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="28">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" ht="17.5" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="28">
         <v>20</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="18.75" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" ht="17.5" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="28">
         <v>21</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="C22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" ht="17.5" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="28">
         <v>22</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="D23" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" ht="17.5" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="28">
         <v>23</v>
       </c>
-      <c r="D7" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" spans="1:12">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="C24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" ht="17.5" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="28">
         <v>24</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" spans="1:12">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="28" t="s">
+      <c r="D25" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" ht="17.5" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="28">
         <v>25</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" spans="1:12">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="28" t="s">
+      <c r="D26" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" ht="17.5" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="28">
+        <v>26</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" ht="17.5" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="28">
         <v>27</v>
       </c>
-      <c r="D10" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" spans="1:12">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="28" t="s">
+      <c r="C28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" ht="17.5" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="28">
         <v>28</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" spans="1:12">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="28" t="s">
+      <c r="D29" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" ht="17.5" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="28">
         <v>29</v>
       </c>
-      <c r="D12" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:12">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="30" t="s">
+      <c r="D30" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" ht="17.5" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="28">
         <v>30</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="28" t="s">
+      <c r="C31" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" ht="17.5" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="28">
         <v>31</v>
       </c>
-      <c r="D14" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" spans="1:12">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="28" t="s">
+      <c r="C32" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" ht="17.5" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="28">
         <v>32</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D33" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" ht="17.5" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="28">
         <v>33</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" spans="1:12">
-      <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="C34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" ht="17.5" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="28">
         <v>34</v>
       </c>
-      <c r="D16" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="28" t="s">
+      <c r="D35" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" ht="17.5" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="28">
         <v>35</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" ht="17.5" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="28">
         <v>36</v>
       </c>
-      <c r="D17" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="28" t="s">
+      <c r="D37" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" ht="17.5" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" s="28">
         <v>37</v>
       </c>
-      <c r="D18" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="28" t="s">
+      <c r="D38" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" ht="17.5" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="28">
         <v>38</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" ht="17.5" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="28">
         <v>39</v>
       </c>
-      <c r="D19" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="28" t="s">
+      <c r="D40" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" ht="17.5" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="28">
         <v>40</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" ht="17.5" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="28">
         <v>41</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" ht="18.75" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="28" t="s">
+      <c r="C42" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" ht="17.5" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="28">
         <v>42</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" ht="17.5" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="28">
         <v>43</v>
       </c>
-      <c r="D21" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" spans="1:4">
-      <c r="A22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="28" t="s">
+      <c r="D44" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" ht="17.5" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="28">
         <v>44</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D45" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" ht="17.5" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="28">
         <v>45</v>
       </c>
-      <c r="D22" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:4">
-      <c r="A23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="30" t="s">
+      <c r="D46" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" ht="17.5" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="28">
         <v>46</v>
       </c>
-      <c r="D23" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" ht="18.75" spans="1:4">
-      <c r="A24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="28" t="s">
+      <c r="D47" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" ht="17.5" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="28">
         <v>47</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D48" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" ht="17.5" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="28">
         <v>48</v>
       </c>
-      <c r="D24" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" ht="18.75" spans="1:4">
-      <c r="A25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="28" t="s">
+      <c r="D49" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" ht="17.5" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="28">
         <v>49</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" ht="18.75" spans="1:4">
-      <c r="A26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="28" t="s">
+      <c r="D50" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" ht="17.5" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="28">
         <v>50</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D51" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" ht="17.5" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" s="28">
         <v>51</v>
       </c>
-      <c r="D26" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" ht="18.75" spans="1:4">
-      <c r="A27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="28" t="s">
+      <c r="D52" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" ht="17.5" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="28">
         <v>52</v>
       </c>
-      <c r="D27" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" ht="18.75" spans="1:4">
-      <c r="A28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="28" t="s">
+      <c r="D53" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" ht="17.5" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" s="28">
         <v>53</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D54" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" ht="17.5" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" s="28">
         <v>54</v>
       </c>
-      <c r="D28" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" ht="17.25" spans="1:4">
-      <c r="A29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="31" t="s">
+      <c r="D55" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" ht="17.5" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="28">
         <v>55</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" ht="18.75" spans="1:4">
-      <c r="A30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="28" t="s">
+      <c r="D56" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" ht="17.5" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" s="28">
         <v>56</v>
       </c>
-      <c r="D30" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" ht="17.25" spans="1:4">
-      <c r="A31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="31" t="s">
+      <c r="D57" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" ht="17.5" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="28">
         <v>57</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="D58" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" ht="17.5" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" s="28">
         <v>58</v>
       </c>
-      <c r="D31" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" ht="18.75" spans="1:4">
-      <c r="A32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="28" t="s">
+      <c r="D59" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" ht="17.5" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" s="28">
         <v>59</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="D60" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" ht="17.5" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="28">
         <v>60</v>
       </c>
-      <c r="D32" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" ht="18.75" spans="1:4">
-      <c r="A33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" s="28" t="s">
+      <c r="D61" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" ht="17.5" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="28">
         <v>61</v>
       </c>
-      <c r="D33" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" ht="18.75" spans="1:4">
-      <c r="A34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" s="28" t="s">
+      <c r="D62" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" ht="17.5" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="28">
         <v>62</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D63" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" ht="17.5" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" s="28">
         <v>63</v>
       </c>
-      <c r="D34" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" ht="18.75" spans="1:4">
-      <c r="A35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B35" s="28" t="s">
+      <c r="D64" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" ht="17.5" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="28">
         <v>64</v>
       </c>
-      <c r="D35" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" ht="18.75" spans="1:4">
-      <c r="A36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="28" t="s">
+      <c r="D65" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" ht="17.5" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" s="28">
         <v>65</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D66" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" ht="17.5" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="28">
         <v>66</v>
       </c>
-      <c r="D36" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" ht="18.75" spans="1:4">
-      <c r="A37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="28" t="s">
+      <c r="D67" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" ht="17.5" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" s="28">
         <v>67</v>
       </c>
-      <c r="D37" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" ht="18.75" spans="1:4">
-      <c r="A38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="28" t="s">
+      <c r="D68" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" ht="17.5" spans="1:4">
+      <c r="A69" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="28">
         <v>68</v>
       </c>
-      <c r="D38" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" ht="18.75" spans="1:4">
-      <c r="A39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="28" t="s">
+      <c r="D69" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" ht="17.5" spans="1:4">
+      <c r="A70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="28">
         <v>69</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D70" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" ht="17.5" spans="1:4">
+      <c r="A71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" s="28">
         <v>70</v>
       </c>
-      <c r="D39" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" ht="18.75" spans="1:4">
-      <c r="A40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B40" s="28" t="s">
+      <c r="D71" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" ht="17.5" spans="1:4">
+      <c r="A72" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" s="28">
         <v>71</v>
       </c>
-      <c r="D40" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" ht="18.75" spans="1:4">
-      <c r="A41" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" s="28" t="s">
+      <c r="D72" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" ht="17.5" spans="1:4">
+      <c r="A73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" s="28">
         <v>72</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D73" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" ht="17.5" spans="1:4">
+      <c r="A74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" s="28">
         <v>73</v>
       </c>
-      <c r="D41" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" ht="18.75" spans="1:4">
-      <c r="A42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="28" t="s">
+      <c r="D74" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" ht="17.5" spans="1:4">
+      <c r="A75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" s="28">
         <v>74</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C75" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" ht="17.5" spans="1:4">
+      <c r="A76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="28">
         <v>75</v>
       </c>
-      <c r="D42" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" ht="18.75" spans="1:4">
-      <c r="A43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="28" t="s">
+      <c r="C76" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" ht="17.5" spans="1:4">
+      <c r="A77" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" s="28">
         <v>76</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C77" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" ht="17.5" spans="1:4">
+      <c r="A78" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" s="28">
         <v>77</v>
       </c>
-      <c r="D43" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" ht="18.75" spans="1:4">
-      <c r="A44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="28" t="s">
+      <c r="D78" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" ht="17.5" spans="1:4">
+      <c r="A79" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="28">
         <v>78</v>
       </c>
-      <c r="D44" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" ht="18.75" spans="1:4">
-      <c r="A45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="28" t="s">
+      <c r="D79" s="29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" ht="17.5" spans="1:4">
+      <c r="A80" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" s="28">
         <v>79</v>
       </c>
-      <c r="D45" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" ht="18.75" spans="1:4">
-      <c r="A46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="28" t="s">
+      <c r="C80" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" ht="17.5" spans="1:4">
+      <c r="A81" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" s="28">
         <v>80</v>
       </c>
-      <c r="D46" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" ht="18.75" spans="1:4">
-      <c r="A47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="28" t="s">
+      <c r="C81" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" ht="17.5" spans="1:4">
+      <c r="A82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" s="28">
         <v>81</v>
       </c>
-      <c r="D47" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" ht="18.75" spans="1:4">
-      <c r="A48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" ht="18.75" spans="1:4">
-      <c r="A49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" ht="18.75" spans="1:4">
-      <c r="A50" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" ht="18.75" spans="1:4">
-      <c r="A51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" ht="18.75" spans="1:4">
-      <c r="A52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" ht="18.75" spans="1:4">
-      <c r="A53" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" ht="18.75" spans="1:4">
-      <c r="A54" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="55" ht="18.75" spans="1:4">
-      <c r="A55" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" ht="18.75" spans="1:4">
-      <c r="A56" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" ht="18.75" spans="1:4">
-      <c r="A57" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" ht="18.75" spans="1:4">
-      <c r="A58" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" ht="18.75" spans="1:4">
-      <c r="A59" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" ht="18.75" spans="1:4">
-      <c r="A60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B60" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" ht="18.75" spans="1:4">
-      <c r="A61" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" ht="18.75" spans="1:4">
-      <c r="A62" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" ht="18.75" spans="1:4">
-      <c r="A63" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" ht="18.75" spans="1:4">
-      <c r="A64" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" ht="18.75" spans="1:4">
-      <c r="A65" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B65" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D65" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" ht="18.75" spans="1:4">
-      <c r="A66" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B66" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D66" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" ht="18.75" spans="1:4">
-      <c r="A67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" ht="18.75" spans="1:4">
-      <c r="A68" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B68" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="D68" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" ht="18.75" spans="1:4">
-      <c r="A69" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B69" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" ht="18.75" spans="1:4">
-      <c r="A70" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B70" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" ht="18.75" spans="1:4">
-      <c r="A71" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" ht="18.75" spans="1:4">
-      <c r="A72" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B72" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D72" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" ht="18.75" spans="1:4">
-      <c r="A73" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B73" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="74" ht="18.75" spans="1:4">
-      <c r="A74" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D74" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" ht="17.25" spans="1:4">
-      <c r="A75" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="D75" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76" ht="17.25" spans="1:4">
-      <c r="A76" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="77" ht="17.25" spans="1:4">
-      <c r="A77" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C77" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" ht="14.25" spans="1:4">
-      <c r="A78" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D78" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" ht="17.25" spans="1:4">
-      <c r="A79" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" ht="17.25" spans="1:4">
-      <c r="A80" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B80" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="C80" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D80" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" ht="17.25" spans="1:4">
-      <c r="A81" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="C81" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D81" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" ht="17.25" spans="1:4">
-      <c r="A82" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="C82" s="31" t="s">
-        <v>122</v>
+      <c r="C82" s="30" t="s">
+        <v>41</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3013,19 +2506,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.23636363636364" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.69166666666667" style="1" customWidth="1"/>
-    <col min="2" max="5" width="14.6916666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.6916666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="74.35" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.23333333333333" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.69090909090909" style="1" customWidth="1"/>
+    <col min="2" max="5" width="14.6909090909091" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.6909090909091" style="1" customWidth="1"/>
+    <col min="7" max="7" width="74.3454545454545" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.23636363636364" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:7">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -3035,17 +2528,17 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7">
       <c r="A2" s="7" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="7" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7">
@@ -3053,22 +2546,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>128</v>
+        <v>47</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7">
@@ -3076,22 +2569,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7">
@@ -3099,22 +2592,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7">
@@ -3122,18 +2615,18 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="12"/>
       <c r="G6" s="9" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:7">
@@ -3141,22 +2634,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>142</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:7">
@@ -3164,22 +2657,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:7">
@@ -3187,22 +2680,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7">
@@ -3210,22 +2703,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:7">
@@ -3233,22 +2726,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>152</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:7">
@@ -3256,22 +2749,22 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>155</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:7">
@@ -3279,16 +2772,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="17"/>
       <c r="F13" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1" spans="1:7">
@@ -3296,18 +2789,18 @@
         <v>12</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="21"/>
       <c r="F14" s="22" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>160</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1" spans="1:7">
@@ -3315,18 +2808,18 @@
         <v>13</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="21"/>
       <c r="F15" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1" spans="1:7">
@@ -3334,23 +2827,23 @@
         <v>14</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="21"/>
       <c r="F16" s="13" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="2:7">
       <c r="B17" s="24" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
